--- a/api/src/main/resources/importaciones/rrhh-novedades.xlsx
+++ b/api/src/main/resources/importaciones/rrhh-novedades.xlsx
@@ -5,23 +5,22 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismael\Downloads\subir\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismael\Documents\calero-app-desktop\api\src\main\resources\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA045739-2002-4DF1-A2DD-211D2BE72FAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8DD1A7-5E40-405F-AA97-1DC5B8E141E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Datos" sheetId="2" r:id="rId2"/>
+    <sheet name="Datos" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>AÑO</t>
   </si>
@@ -35,9 +34,6 @@
     <t>Sobresueldos, comisiones y otras remuneraciones gravadas de I.Renta (materia gravada de seguridad social)</t>
   </si>
   <si>
-    <t>Otros ingresos gravados de I.Renta (maeteria NO gravada de seguridad social)</t>
-  </si>
-  <si>
     <t>Décimo tercer sueldo</t>
   </si>
   <si>
@@ -59,40 +55,34 @@
     <t>Impuesto a la renta asumido por el empleador</t>
   </si>
   <si>
-    <t xml:space="preserve">0101328524   </t>
-  </si>
-  <si>
     <t>Sobresueldos, comisiones y otras remuneraciones gravadas de I.Renta (materia NO gravada de seguridad social)</t>
   </si>
   <si>
-    <t>1103779078</t>
-  </si>
-  <si>
-    <t>0703166934</t>
-  </si>
-  <si>
-    <t>1103853444</t>
-  </si>
-  <si>
-    <t>1103915706</t>
-  </si>
-  <si>
-    <t>1104418049</t>
-  </si>
-  <si>
-    <t>0906049507</t>
-  </si>
-  <si>
-    <t>0906297486</t>
-  </si>
-  <si>
-    <t>1100449204</t>
-  </si>
-  <si>
-    <t>PERIODO</t>
-  </si>
-  <si>
-    <t>2026-01</t>
+    <t>1790715949001</t>
+  </si>
+  <si>
+    <t>0190151530001</t>
+  </si>
+  <si>
+    <t>0300855368001</t>
+  </si>
+  <si>
+    <t>1760000740001</t>
+  </si>
+  <si>
+    <t>1760003410001</t>
+  </si>
+  <si>
+    <t>1791131606001</t>
+  </si>
+  <si>
+    <t>1751136138001</t>
+  </si>
+  <si>
+    <t>1751126138001</t>
+  </si>
+  <si>
+    <t>1751134138001</t>
   </si>
 </sst>
 </file>
@@ -157,7 +147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -183,9 +173,6 @@
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -593,102 +580,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="39.28515625" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" s="10" customFormat="1" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="5">
-        <v>800</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5">
-        <v>100</v>
-      </c>
-      <c r="F2" s="5">
-        <v>4368.96</v>
-      </c>
-      <c r="G2" s="5">
-        <v>353.22</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>3519.66</v>
-      </c>
-      <c r="K2" s="5">
-        <f>(C2+D2)*0.0945</f>
-        <v>75.599999999999994</v>
-      </c>
-      <c r="L2" s="5">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="3"/>
@@ -719,28 +612,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -787,7 +680,7 @@
         <v>2023</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>1200</v>
@@ -857,40 +750,18 @@
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2200</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="1">
-        <v>43.92</v>
-      </c>
-      <c r="G5" s="1">
-        <v>169.98</v>
-      </c>
-      <c r="H5" s="2">
-        <v>43.9</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>671.22</v>
-      </c>
-      <c r="K5" s="1">
-        <v>600</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -898,32 +769,32 @@
         <v>2023</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1">
-        <v>3000</v>
+        <v>2200</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1">
-        <v>3559.49</v>
+        <v>43.92</v>
       </c>
       <c r="G6" s="1">
-        <v>340</v>
+        <v>169.98</v>
       </c>
       <c r="H6" s="2">
-        <v>2862.65</v>
+        <v>43.9</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>671.22</v>
       </c>
       <c r="K6" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -935,23 +806,23 @@
         <v>2023</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D7" s="1">
-        <v>342.07</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
-        <v>578.26</v>
+        <v>3559.49</v>
       </c>
       <c r="G7" s="1">
-        <v>125.43</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
+        <v>340</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2862.65</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -960,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -972,20 +843,20 @@
         <v>2023</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>342.07</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
-        <v>505</v>
+        <v>578.26</v>
       </c>
       <c r="G8" s="1">
-        <v>79.5</v>
+        <v>125.43</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -994,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>1074.6400000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1009,20 +880,20 @@
         <v>2023</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1">
-        <v>48.75</v>
+        <v>505</v>
       </c>
       <c r="G9" s="1">
-        <v>26.5</v>
+        <v>79.5</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -1031,10 +902,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>47.19</v>
+        <v>1074.6400000000001</v>
       </c>
       <c r="K9" s="1">
-        <v>2000</v>
+        <v>900</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1046,41 +917,78 @@
         <v>2023</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="D10" s="1">
-        <v>443.68</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
+        <v>48.75</v>
+      </c>
+      <c r="G10" s="1">
+        <v>26.5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>47.19</v>
+      </c>
+      <c r="K10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1">
+        <v>15000</v>
+      </c>
+      <c r="D11" s="1">
+        <v>443.68</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
         <v>178.47</v>
       </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>3500</v>
       </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1"/>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/api/src/main/resources/importaciones/rrhh-novedades.xlsx
+++ b/api/src/main/resources/importaciones/rrhh-novedades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismael\Documents\calero-app-desktop\api\src\main\resources\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8DD1A7-5E40-405F-AA97-1DC5B8E141E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8019E2-A292-4A99-96E0-D5E0D0B250DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/api/src/main/resources/importaciones/rrhh-novedades.xlsx
+++ b/api/src/main/resources/importaciones/rrhh-novedades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismael\Documents\calero-app-desktop\api\src\main\resources\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8019E2-A292-4A99-96E0-D5E0D0B250DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD24BBD8-C79E-426A-9D30-1DDB17E362CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>AÑO</t>
   </si>
@@ -58,31 +58,34 @@
     <t>Sobresueldos, comisiones y otras remuneraciones gravadas de I.Renta (materia NO gravada de seguridad social)</t>
   </si>
   <si>
-    <t>1790715949001</t>
-  </si>
-  <si>
-    <t>0190151530001</t>
-  </si>
-  <si>
-    <t>0300855368001</t>
-  </si>
-  <si>
-    <t>1760000740001</t>
-  </si>
-  <si>
-    <t>1760003410001</t>
-  </si>
-  <si>
-    <t>1791131606001</t>
-  </si>
-  <si>
-    <t>1751136138001</t>
-  </si>
-  <si>
-    <t>1751126138001</t>
-  </si>
-  <si>
-    <t>1751134138001</t>
+    <t>1234567891001</t>
+  </si>
+  <si>
+    <t>1234567892001</t>
+  </si>
+  <si>
+    <t>1234567893001</t>
+  </si>
+  <si>
+    <t>1234567894001</t>
+  </si>
+  <si>
+    <t>1234567895001</t>
+  </si>
+  <si>
+    <t>1234567896001</t>
+  </si>
+  <si>
+    <t>1234567897001</t>
+  </si>
+  <si>
+    <t>1234567898001</t>
+  </si>
+  <si>
+    <t>1234567899001</t>
+  </si>
+  <si>
+    <t>2026-12</t>
   </si>
 </sst>
 </file>
@@ -581,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="3"/>
@@ -637,8 +640,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>2023</v>
+      <c r="A2" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>12</v>
@@ -676,8 +679,8 @@
       <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2023</v>
+      <c r="A3" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>13</v>
@@ -713,11 +716,11 @@
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>2023</v>
+      <c r="A4" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
         <v>1400</v>
@@ -750,51 +753,73 @@
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2200</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="F5" s="1">
+        <v>43.92</v>
+      </c>
+      <c r="G5" s="1">
+        <v>169.98</v>
+      </c>
+      <c r="H5" s="2">
+        <v>43.9</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>671.22</v>
+      </c>
+      <c r="K5" s="1">
+        <v>600</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>2023</v>
+      <c r="A6" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1">
-        <v>43.92</v>
+        <v>3559.49</v>
       </c>
       <c r="G6" s="1">
-        <v>169.98</v>
+        <v>340</v>
       </c>
       <c r="H6" s="2">
-        <v>43.9</v>
+        <v>2862.65</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>671.22</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -802,27 +827,27 @@
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>2023</v>
+      <c r="A7" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>342.07</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
-        <v>3559.49</v>
+        <v>578.26</v>
       </c>
       <c r="G7" s="1">
-        <v>340</v>
-      </c>
-      <c r="H7" s="2">
-        <v>2862.65</v>
+        <v>125.43</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -831,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -839,24 +864,24 @@
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>2023</v>
+      <c r="A8" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="D8" s="1">
-        <v>342.07</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
-        <v>578.26</v>
+        <v>505</v>
       </c>
       <c r="G8" s="1">
-        <v>125.43</v>
+        <v>79.5</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -865,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>0</v>
+        <v>1074.6400000000001</v>
       </c>
       <c r="K8" s="1">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -876,24 +901,24 @@
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>2023</v>
+      <c r="A9" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1">
-        <v>505</v>
+        <v>48.75</v>
       </c>
       <c r="G9" s="1">
-        <v>79.5</v>
+        <v>26.5</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -902,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>1074.6400000000001</v>
+        <v>47.19</v>
       </c>
       <c r="K9" s="1">
-        <v>900</v>
+        <v>2000</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -913,24 +938,24 @@
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>2023</v>
+      <c r="A10" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>443.68</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
-        <v>48.75</v>
+        <v>178.47</v>
       </c>
       <c r="G10" s="1">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -939,52 +964,15 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>47.19</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
       </c>
       <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1">
-        <v>15000</v>
-      </c>
-      <c r="D11" s="1">
-        <v>443.68</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1">
-        <v>178.47</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>3500</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
